--- a/affiliate_data/สินค้าขายดี.xlsx
+++ b/affiliate_data/สินค้าขายดี.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>❤️ส่งด่วน1วัน รีวิวเยอะสุด 🙏เกรดพรีเมี่ยม ทุเรียนหมอนทองจันทบุรี แกะเนื้อล้วน พร้อมทาน 🚚ส่งรถเย็น</v>
+        <v>ไม้เซลฟี่บลูทูธ รุ่น K28P หมุนได้ 360 องศา พร้อมรีโมทบลูทูธ ยืดได้1.75ซม.ขาตั้งTripod พร้อมส่ง</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-7rd63-m70pki5sxt3db3.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>469.00</v>
+        <v>132.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 30พัน+ ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/22414045290</v>
+        <v>https://shopee.co.th/product/0/22390716846</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/LkU9ZKNZy</v>
+        <v>https://s.shopee.co.th/2BCIORE2pV</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -480,37 +480,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>แชมพูปิดผมขาวหอมเกศ พร้อมบำรุงเส้นผม 990 บาท (แบบขวด 300 มล.)</v>
+        <v>adidas Football Liverpool FC 25/26 Home Jersey Men Red JV6423</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mos57zj9wmq7bb.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823rg-mozkz8y7hngh5f.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>549.00</v>
+        <v>2175.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 70พัน+ ชิ้น</v>
+        <v>ขายได้ 1พัน+ ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/17909604787</v>
+        <v>https://shopee.co.th/product/0/57752875499</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/4ftTJXDABc</v>
+        <v>https://s.shopee.co.th/2g8YzMJyhA</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -518,37 +518,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Intensive Ginseng Hya Vitamin Night Cream ครีมโสม(ยกเลิกของแถม)</v>
+        <v>TOTORI หมอน รุ่น คลาวด์(Cloud model) , หมอนหนุน</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mnfkz2p874sm88.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m7dtemqzvjru7c.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>290.00</v>
+        <v>124.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 90พัน+ ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://shopee.co.th/product/0/23758244422</v>
+        <v>https://shopee.co.th/product/0/28979758342</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/3LO5j5R2SO</v>
+        <v>https://s.shopee.co.th/17noSeEeX</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -556,37 +556,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>TOTORI หมอน รุ่น คลาวด์(Cloud model) , หมอนหนุน</v>
+        <v>ใหม่ ! Oriental Princess ครีมทาผิว Moisturising Body Lotion 390 ml</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasl-m7dtemqzvjru7c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mo95qr9hd6o5aa.webp</v>
       </c>
       <c r="D5" t="str">
-        <v>124.00</v>
+        <v>148.00</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="G5" t="str">
-        <v>ขายได้ 90พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>https://shopee.co.th/product/0/28979758342</v>
+        <v>https://shopee.co.th/product/0/7578431882</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/9ALsfo8opb</v>
+        <v>https://s.shopee.co.th/5L9KAGRQPk</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>GOOJODOQ Gfs001 พัดลมพกพา พัดลม Type C พัดลมไอเย็น พร้อมจอแสดงผล พัดลมมือถือ พัดลมมือถือ</v>
+        <v>รองเท้าแตะ แบรนด์ MARCO รุ่น G1005 คาดเข็มขัด หนังนิ่ม</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mh0cvjy8shlb85.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-7ra32-mbi09g90wacl3d.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>529.00</v>
+        <v>167.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 6พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/41959397717</v>
+        <v>https://shopee.co.th/product/0/26288089781</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/4Va37Ea0E3</v>
+        <v>https://s.shopee.co.th/110L0IqEw2</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -632,37 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>[Best Seller] Paloy - PL2360 Camellia Top เสื้อแขนยาว ทรงเข้ารูป ปลายแขนแต่งดอกคาเมลเลีย</v>
+        <v>❤️ส่งด่วน1วัน รีวิวเยอะสุด 🙏เกรดพรีเมี่ยม ทุเรียนหมอนทองจันทบุรี แกะเนื้อล้วน พร้อมทาน 🚚ส่งรถเย็น</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mo97h5l1bs3q29.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0o-mcoacmrgvbz293.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>490.00</v>
+        <v>489.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>17</v>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/27832497926</v>
+        <v>https://shopee.co.th/product/0/22414045290</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/9zuzfLNeqN</v>
+        <v>https://s.shopee.co.th/2LViakttXG</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -676,13 +676,13 @@
         <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mdyso1l1mbcz05.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>199.00</v>
+        <v>187.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G8" t="str">
         <v>ขายได้ 100พัน+ ชิ้น</v>
@@ -694,7 +694,7 @@
         <v>https://shopee.co.th/product/0/23525917652</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/60Oqtzn3lm</v>
+        <v>https://s.shopee.co.th/7VDokFjv1Z</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -708,37 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>[บอสหนุ่ม] ยาสีฟันขิงขิง 1แถม1 ยาสีฟันสมุนไพร ลดกลิ่นปาก ฟันขาว ฟันแข็งแรง สินค้าจากบริษัทโดยตรง พร้อมจัดส่ง</v>
+        <v>แชมพูปิดผมขาวหอมเกศ พร้อมบำรุงเส้นผม 990 บาท (แบบขวด 300 มล.)</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-22090-obf5vp7h6xhved.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mos57zj9wmq7bb.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>290.00</v>
+        <v>506.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 90พัน+ ชิ้น</v>
+        <v>ขายได้ 70พัน+ ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/16086302672</v>
+        <v>https://shopee.co.th/product/0/17909604787</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/3LO5j64Dvb</v>
+        <v>https://s.shopee.co.th/7pqf8rqclS</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -746,31 +746,31 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>GOOJODOQ Gfs006 พัดลมพกพา 4000mah พัดลม Type C หมอกเย็น พัดลมไอเย็น 100 ระดับ พัดลมมือถือ</v>
+        <v>[Best Seller] Paloy - PL2360 Camellia Top เสื้อดอกคามิเลีย เสื้อแขนยาว ทรงเข้ารูป ปลายแขนแต่งดอกคามิเลีย</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mh0da82x1edqc9.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mo97h5l1bs3q29.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>449.00</v>
+        <v>490.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>62</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 5พัน+ ชิ้น</v>
+        <v>ขายได้ 20พัน+ ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/40959376984</v>
+        <v>https://shopee.co.th/product/0/27832497926</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/7AaoI8znxR</v>
+        <v>https://s.shopee.co.th/8KmvjmzNP4</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -784,19 +784,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>[ขายดี NO.1][พุทรานมสด]{แช่อิ่ม] แบรนด์ชาววังเจ้าดังในตต [หวานฉ่ำ กรอบ อร่อย}ฟรีพริกเกลือ5</v>
+        <v>mvp sprot เสื้อกีฬา เสื้อรัดรูปแขนยาวออกกำลังกาย แจ็คเก็ตแขนยาวมีซิปรูด เสื้อสปอร์ตแขนยาว แจ็คเก็ตกันแดด ป้องกันรังสียูว</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mon8ifmnuy9t01.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-7rdy3-mdhaxs8drqhw03.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>70.00</v>
+        <v>139.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="G11" t="str">
         <v>ขายได้ 40พัน+ ชิ้น</v>
@@ -805,16 +805,16 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/28518135279</v>
+        <v>https://shopee.co.th/product/0/21001732437</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/7fX4t457U1</v>
+        <v>https://s.shopee.co.th/AAEZv9zGtc</v>
       </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -822,31 +822,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Life Plus โพรไบโอ18 Life Plus ProBio18 Probiotic 2 กรัม ชนิดกรอกปาก(LPCAD)</v>
+        <v>[บอสหนุ่ม] ยาสีฟันขิงขิง 1แถม1 ยาสีฟันสมุนไพร ลดกลิ่นปาก ฟันขาว ฟันแข็งแรง สินค้าจากบริษัทโดยตรง พร้อมจัดส่ง</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhpurrwf2adi2f.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-22090-obf5vp7h6xhved.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>498.00</v>
+        <v>290.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="G12" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 90พัน+ ชิ้น</v>
       </c>
       <c r="H12" t="str">
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/25613687442</v>
+        <v>https://shopee.co.th/product/0/16086302672</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/902STWApxE</v>
+        <v>https://s.shopee.co.th/1BJlCccgqJ</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -860,31 +860,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>โปรพิเศษ🔥สครับสปาบ้านทุ่ง 2 กป. ✨299 บาท สินค้าแท้ 100%✨</v>
+        <v>[ กด 2 ชิ้นเพื่อรับโปร 1 แถม 2 แถมหลังบ้านอัตโนมัติ ] MAGIC LIP OIL เมจิก ลิปออยล์ 3.5 กรัม</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mi4a58iyws1s2e.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mowteyfclf63d6.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>229.00</v>
+        <v>199.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 100พัน+ ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/25978598917</v>
+        <v>https://shopee.co.th/product/0/25808041101</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/AUrGGHCHAa</v>
+        <v>https://s.shopee.co.th/17noTtVOT</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -898,31 +898,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>GOOJODOQ Gfs007 Mini พัดลมพกพา 4000mah พัดลม Type C พร้อมจอแสดงผล พัดลมไอเย็น 100 ระดับ พัดลมมือถือ</v>
+        <v>Life Plus โพรไบโอ18 Life Plus ProBio18 Probiotic 2 กรัม ชนิดกรอกปาก(LPCAD)</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mh0c1qxjicr3a0.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mhpurrwf2adi2f.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>279.00</v>
+        <v>518.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 20พัน+ ชิ้น</v>
+        <v>ขายได้ 10พัน+ ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/28841463764</v>
+        <v>https://shopee.co.th/product/0/25613687442</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/2qRp8BpuaJ</v>
+        <v>https://s.shopee.co.th/AUrQJmLrDP</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -936,37 +936,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>(ร้านบริษัท) ลูน่าอายครีม (ลดริ้วรอย แก้ขอบตาคล้ำ ฟื้นฟูใต้ตา กระชับใต้ตา หัวนวดเก็บความเย็น )</v>
+        <v>สบู่เฟย์ด้า ของแท้ FayDa planktonsoap สบู่รักษาสิว ขนาด 50 กรัม</v>
       </c>
       <c r="C15" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnfg8o9cv7k53a.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasj-m9xtvc28jzse8b.webp</v>
       </c>
       <c r="D15" t="str">
-        <v>178.00</v>
+        <v>109.00</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>35</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 200พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>https://shopee.co.th/product/0/20670788897</v>
+        <v>https://shopee.co.th/product/0/25059198086</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/4AxCidri6N</v>
+        <v>https://s.shopee.co.th/3Vhfyutix2</v>
       </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -974,37 +974,37 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>เจลกำจัดมด ANTIANT แอนตี้แอนท์ [ของแท้จากร้าน Antiant Thailand]</v>
+        <v>GQ Everyday Sport Polo เสื้อโปโล สไตล์สปอร์ต ผ้าใส่สบาย ระบายอากาศดี</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mibu5xev4kjq01.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-mbp0n7oq2zmv5d.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>83.00</v>
+        <v>265.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 100พัน+ ชิ้น</v>
+        <v>ขายได้ 40พัน+ ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/21685245804</v>
+        <v>https://shopee.co.th/product/0/28126669065</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/1gFrk35u0S</v>
+        <v>https://s.shopee.co.th/2BCIOT2vOS</v>
       </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -1012,31 +1012,31 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>GQ Everyday Running &amp; Training Votex-T​ เสื้อวิ่งออกกำลังกาย​</v>
+        <v>Hello Polo รองเท้าแฟชั่นผู้หญิง ดีไซน์เรียบง่าย พื้นหนานุ่ม กันลื่นและทนทาน คลายเมื่อยเท้า วัสดุ EVA แฟชั่นฤดูร้อนHP8067</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mjip0026tgquda.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mop5uzmbsikh11.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>189.00</v>
+        <v>159.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 40พัน+ ชิ้น</v>
+        <v>ขายได้ 710 ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/44170564543</v>
+        <v>https://shopee.co.th/product/0/52809984572</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/2qRp8C9z9j</v>
+        <v>https://s.shopee.co.th/1LdBOwFAhJ</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1050,37 +1050,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>iMI Powerbank 20000mAh มินิ พกพา ชาร์จเร็ว 22.5W สายชาร์จในตัว แขวนกระเป๋า ขึ้นเครื่องบินได้ รับประกัน1ปี</v>
+        <v>GOOJODOQ Gfs007 Mini พัดลมพกพา 4000mah พัดลม Type C พร้อมจอแสดงผล พัดลมไอเย็น 100 ระดับ พัดลมมือถือ</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mmiivnqd2s5f9c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mh0c1qxjicr3a0.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>699.00</v>
+        <v>279.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G18" t="str">
-        <v>ขายได้ 4พัน+ ชิ้น</v>
+        <v>ขายได้ 20พัน+ ชิ้น</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/56658053805</v>
+        <v>https://shopee.co.th/product/0/28841463764</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/9fI9GktWjw</v>
+        <v>https://s.shopee.co.th/5L9KAI8XMI</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -1088,19 +1088,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>ดีดีครีมกันแดดแตงโม แบบ 1 กล่อง 6 ซอง [เนียนใส อัพผิวไบร์ท] Jula's Herb จุฬาเฮิร์บ</v>
+        <v>กางเกงออกกำลังกายขาสั้นผู้หญิง กางเกงโยคะ กางเกงขาสั้น</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasb-m0o80foxz0ze52.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mimgjwlflkw4c8.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>290.00</v>
+        <v>140.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G19" t="str">
         <v>ขายได้ 10พัน+ ชิ้น</v>
@@ -1109,10 +1109,10 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/28662575794</v>
+        <v>https://shopee.co.th/product/0/53452439323</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/AUrGGI0FoC</v>
+        <v>https://s.shopee.co.th/7fXEwa9HLg</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1126,37 +1126,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>น้ำตาลหล่อฮังก๊วย 0แคลลอรี่ (มี อ.ย รับรอง) ขนาด500กรัม หวานเท่ากับน้ำตาล1:1</v>
+        <v>[48 ฟรี 12] WHISKAS วิสกัส อาหารเปียกแมว ลูกแมว แมวโต แมวสูงวัย เลือกรสชาติได้ 80ก.</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgkntn0w0b2j98.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moxpql9rzqizdd.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>128.00</v>
+        <v>864.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 100พัน+ ชิ้น</v>
+        <v>ขายได้ 30พัน+ ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/25432214222</v>
+        <v>https://shopee.co.th/product/0/40117314945</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/AKXq3z9kzB</v>
+        <v>https://s.shopee.co.th/902cX2CrgK</v>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1164,31 +1164,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>[Best Seller] Paloy - PL0082 กางเกงยีนส์เอวต่ำ ขากระบอกกลาง แต่งเฟด</v>
+        <v>GQ Everyday T-Shirt เสื้อยืดผ้านุ่ม ยืดไม่ย้วย มี 17 สี คุณภาพเกินราคา ที่สุดแห่งความสบาย ระบายอากาศ ไม่มีป้ายคอ ไม่คัน</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mojf3rwww7wg6b.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rask-madn81zxp06u20.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>750.00</v>
+        <v>164.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 10พัน+ ชิ้น</v>
+        <v>ขายได้ 200พัน+ ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/26621690776</v>
+        <v>https://shopee.co.th/product/0/18284848416</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/7VDegmRYTD</v>
+        <v>https://s.shopee.co.th/BRE0nuOM6</v>
       </c>
       <c r="K21" t="str">
         <v/>
